--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_preneta_a_2021_coquimbo.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_preneta_a_2021_coquimbo.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:24</t>
+    <t xml:space="preserve">2026-09-24 01:15</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -730,19 +730,19 @@
         <v>19</v>
       </c>
       <c r="C10" s="2" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="D10" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E10" s="2" t="n">
         <v>0.21</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>-0.19</v>
+        <v>-0.2</v>
       </c>
     </row>
     <row r="11">
@@ -753,19 +753,19 @@
         <v>19</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>-0.14</v>
+        <v>-0.09</v>
       </c>
       <c r="D11" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E11" s="2" t="n">
         <v>0.16</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>-0.3</v>
+        <v>-0.25</v>
       </c>
     </row>
     <row r="12">
@@ -776,19 +776,19 @@
         <v>19</v>
       </c>
       <c r="C12" s="2" t="n">
-        <v>0.06</v>
+        <v>0.04</v>
       </c>
       <c r="D12" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E12" s="2" t="n">
         <v>0.15</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="G12" s="2" t="n">
-        <v>-0.08</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="13">
@@ -799,19 +799,19 @@
         <v>19</v>
       </c>
       <c r="C13" s="2" t="n">
-        <v>0.1</v>
+        <v>0.06</v>
       </c>
       <c r="D13" s="2" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>0.06</v>
+        <v>0.01</v>
       </c>
     </row>
     <row r="14">
